--- a/zooniverse-project/tracker.xlsx
+++ b/zooniverse-project/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seattleaquarium-my.sharepoint.com/personal/m_williams_seattleaquarium_org/Documents/Documents/GitHub/CCR_benthic_analyses/zooniverse-project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Seattle Aquarium Dropbox\Coastal_Climate_Resilience\GitHub\CCR_benthic_analyses\zooniverse-project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="6_{D88F6E4D-1BB0-485D-BA81-DFBE5089B10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F1151E-1144-4394-85F6-20DDACDE3533}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3ED054-3CC7-4524-81C3-ED2A6F168358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,7 @@
     <sheet name="Export Log" sheetId="3" r:id="rId2"/>
     <sheet name="Summary Dashboard" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="91">
   <si>
     <t>Track transects, subject sets, image counts, upload status &amp; script versions</t>
   </si>
@@ -307,6 +306,9 @@
   </si>
   <si>
     <t>PKB_S25_T3</t>
+  </si>
+  <si>
+    <t>PKB_S25_T2</t>
   </si>
 </sst>
 </file>
@@ -2017,18 +2019,38 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="2"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="32"/>
+      <c r="A35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="32">
+        <v>45883</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E35" s="2">
+        <v>138908</v>
+      </c>
+      <c r="F35" s="2">
+        <v>60</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H35" s="32">
+        <v>46278</v>
+      </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="7"/>
+      <c r="K35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="36" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="4"/>
@@ -3131,7 +3153,7 @@
       </c>
       <c r="B3" s="13">
         <f>COUNTA('Subject Set Tracker'!A5:A211)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="60" t="s">
         <v>34</v>
@@ -3141,7 +3163,7 @@
     <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.55000000000000004">
       <c r="D4" s="62">
         <f ca="1">TODAY()</f>
-        <v>46245</v>
+        <v>46278</v>
       </c>
       <c r="E4" s="57"/>
     </row>
@@ -3151,7 +3173,7 @@
       </c>
       <c r="B5" s="13">
         <f>SUM('Subject Set Tracker'!F5:F211)</f>
-        <v>1180</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -3166,7 +3188,7 @@
       </c>
       <c r="B7" s="13">
         <f>SUM('Subject Set Tracker'!G5:G211)</f>
-        <v>57900</v>
+        <v>60900</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>14</v>
@@ -3204,7 +3226,7 @@
       </c>
       <c r="B11" s="13">
         <f>COUNTIF('Subject Set Tracker'!K5:K211,"In Progress")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>38</v>
